--- a/diseases/d071/2020-2025.xlsx
+++ b/diseases/d071/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36248,7 +36248,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d071/2020-2025.xlsx
+++ b/diseases/d071/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36248,7 +36248,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d071/2020-2025.xlsx
+++ b/diseases/d071/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36248,7 +36248,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d071/2020-2025.xlsx
+++ b/diseases/d071/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36248,7 +36248,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d071/2020-2025.xlsx
+++ b/diseases/d071/2020-2025.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25160,7 +25160,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26744,7 +26744,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29120,7 +29120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31496,7 +31496,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33080,7 +33080,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36248,7 +36248,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37040,7 +37040,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
